--- a/input-test.xlsx
+++ b/input-test.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20401"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B840E679-B726-4261-8AE9-27CF828E768A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83242AF3-D301-4AE9-87EE-9C5C3425C936}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -227,7 +227,7 @@
     <t>More6</t>
   </si>
   <si>
-    <t>totem mini finessed.ies</t>
+    <t>Giulius Asym DOWN.ies</t>
   </si>
 </sst>
 </file>
